--- a/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M08/second/CF_M08_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M08/second/CF_M08_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9677</v>
       </c>
       <c r="D13" t="n">
+        <v>0.9091</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9167999999999999</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>Una empresa ha de poder dar de alta una ruta para vincularla a sus productos.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -772,10 +776,6 @@
           <t>A company must be able to register a route to link it to its products.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,10 +806,6 @@
           <t>El sistema ha de contar con un sistema de afiliación/planes para empresas que quieran tener ciertas ventajas (cuenta con tres planes: gratuito, básico y premium).</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Constraint</t>
@@ -823,10 +819,6 @@
           <t>The system should have three different membership plans: free, basic and premium.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -857,10 +849,6 @@
           <t>El sistema ha de permitir cerrar sesión a los usuarios.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -874,10 +862,6 @@
           <t>The system must allow users to log out.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -908,10 +892,6 @@
           <t>Una empresa ha de poder dar de alta un producto y que éste sea visible en su perfil/página pública.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -925,10 +905,6 @@
           <t>A company must be able to register a product and have it visible on its profile/page public.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -959,14 +935,11 @@
           <t>Pruebas de compatibilidad que demuestren funcionalidad en los principales navegadores y dispositivos móviles.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_26</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -980,14 +953,11 @@
           <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M08_R25</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1018,14 +988,11 @@
           <t>Comprobar que solo los usuario empresa puede acceder a sus productos/rutas/perfil.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_30</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1039,14 +1006,11 @@
           <t>Verify that only Business Users can access their products/routes/profile.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M08_R29</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1077,10 +1041,6 @@
           <t>Todo producto ha de tener una ruta predeterminada en la que el usuario lo devuelve por su cuenta y con sus propios medios.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1094,10 +1054,6 @@
           <t>Every product must have a predetermined route in which the user returns it on his own account and with his own means.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1128,14 +1084,11 @@
           <t>El sistema estará tanto en español como en inglés (verificados por un traductor).</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_16</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1149,14 +1102,11 @@
           <t>The system should support Spanish and English (verified by a translator).</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M08_R15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1187,10 +1137,6 @@
           <t>Un usuario ha de poder devolver un producto dado de alta en una empresa mediante el uso de sus rutas.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1204,10 +1150,6 @@
           <t>A user must be able to return a product registered in a company throug the use of its routes.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1238,14 +1180,11 @@
           <t>El sistema debe pasar auditorías de seguridad sin vulnerabilidades críticas.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1259,14 +1198,11 @@
           <t xml:space="preserve"> The system must pass security audits data without critical vulnerabilities.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M08_R19</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1297,10 +1233,6 @@
           <t>Toda ruta ha de tener un presupuesto asociado (puede ser 0) el cual el usuario ha de poder pagar mediante el uso del sistema a la hora de retornar el producto.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1314,10 +1246,6 @@
           <t>Every route must have an associated budget (can be 0) which the user must be able to pay using the system when returning the product.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1348,10 +1276,6 @@
           <t>El sistema ha de permitir a usuarios logueados o no ver los perfiles de las distintas empresas así como sus productos.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1365,10 +1289,6 @@
           <t>The system must allow users logged-in or non-logged-in to see the profiles and products of the different companies.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1399,10 +1319,6 @@
           <t>Una empresa ha de poder modificar su perfil/página pública en todo momento, al igual que previsualizarlo mientras está editando.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1416,10 +1332,6 @@
           <t>A company must be able to modify its public profile/page at any time and preview it while editing</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1450,14 +1362,11 @@
           <t>Realización de pruebas de usabilidad con al menos 10 usuarios representativos, logrando una puntuación de satisfacción mínima de 8/10.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1471,14 +1380,11 @@
           <t>Performance of usability tests with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M08_R17</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1514,9 +1420,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1540,8 +1443,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1577,9 +1478,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1598,9 +1496,6 @@
           <t>CF_M08_C05</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1636,9 +1531,6 @@
           <t>C_08</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1662,8 +1554,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1694,14 +1584,11 @@
           <t>Capacidad para aumentar los recursos del servidor y mantener el rendimiento con un incremento del 50% en la carga de trabajo.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_28</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1715,14 +1602,11 @@
           <t>Capacity to increase the resources of the server and maintain performance with a 50% increase in workload.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M08_R27</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1753,14 +1637,11 @@
           <t>Monitoreo de tiempo de actividad que demuestre un uptime del 99.9% y pruebas de recuperación de desastres que cumplan con el tiempo de recuperación especificado.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_22</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1774,14 +1655,11 @@
           <t>Uptime monitoring demonstrating 99.9% uptime and disaster recovery testing that meets the specified recovery time.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M08_R21</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1812,10 +1690,6 @@
           <t>El sistema ha de poder autenticar a usuarios existentes a través del email.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1829,10 +1703,6 @@
           <t>The system must be able to authenticate existing users through email.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1868,9 +1738,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1889,9 +1756,6 @@
           <t>CF_M08_C04</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1927,9 +1791,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1953,8 +1814,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1985,10 +1844,6 @@
           <t>Un usuario puede ser tanto un donante como una empresa.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2002,10 +1857,6 @@
           <t>A user can be both a donor and a company.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2036,10 +1887,6 @@
           <t>El sistema ha de permitir registrar usuarios nuevos al sistema.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2053,10 +1900,6 @@
           <t>The system must allow new users to register in the system.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2092,9 +1935,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2118,8 +1958,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2150,10 +1988,6 @@
           <t>Una empresa ha de tener acceso al dashboard del sistema para poder utilizar las distintas funcionalidades internas e información adicional (estadísticas, valores, etc.).</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2167,10 +2001,6 @@
           <t>A company must have access to the system dashboard to be able to use the different ones internal functionalities and additional information (statistics, values, etc.).</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2201,10 +2031,6 @@
           <t>El sistema ha de poder guardar todas las imágenes de todos los productos/usuarios del sistema.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2218,10 +2044,6 @@
           <t>The system must be able to save all the images of all the products and users of the system.</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2252,14 +2074,11 @@
           <t>Documentación completa y actualizada, y tiempo promedio de implementación de actualizaciones y resolución de problemas no superior a 2 horas.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>R_24</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2273,14 +2092,11 @@
           <t>Complete and up-to-date documentation, and average implementation time for updates and problem resolution not exceeding 2 hours.</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CF_M08_R23</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2316,9 +2132,6 @@
           <t>C_07</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2342,8 +2155,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2379,9 +2190,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2405,8 +2213,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
